--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.9</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78e7dca5038b723</t>
+          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Chinese Mandarin Speaker)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.6</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38690ace7c9a024c</t>
+          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
+          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>StationMD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maplewood, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
+          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
+          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bd622b5093a1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Data</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cloudforce</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>National Harbor, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Cloud Engineer - Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Cloudforce</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>National Harbor, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
         </is>
       </c>
     </row>
@@ -958,35 +958,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
+          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Integration Developer</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Atash Enterprises LLC</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a88924ef9fe1db</t>
+          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
         </is>
       </c>
     </row>
@@ -1168,35 +1168,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
         </is>
       </c>
     </row>
@@ -1213,42 +1213,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c524210e9570a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c93acf42a0d223</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=922392e2e4746be9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Full Stack Customer Data Developer</t>
+          <t>Java AWS Developer - Face to Face Interview</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Core Alliance Group Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Dataflow, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
+          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
         </is>
       </c>
     </row>
@@ -1378,25 +1378,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=922392e2e4746be9</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
+          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java AWS Developer - Face to Face Interview</t>
+          <t>Canoe Platform Data / Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Core Alliance Group Inc.</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f715405c24533f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Solifi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Canoe Platform Data / Integration Engineer</t>
+          <t>Digital Site Reliability Sr Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>HBase, Scala, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
+          <t>https://www.indeed.com/viewjob?jk=02dd332b5bab760b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Digital Site Reliability Sr Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HBase, Scala, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02dd332b5bab760b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineer - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WorkCog</t>
+          <t>WesTech Engineering, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Comfort, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, MLOps, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f795da03d0dac54f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Solifi</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Solutions Associate Senior - DART</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c45d7cba759cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WesTech Engineering, LLC</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,137 +1861,137 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud DevAI Ops Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Radiant Logistics</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, Azure, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3939a216a2d74</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7d8d9f65b102c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering — Gateway Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, HBase, Kafka, Oracle, PostgreSQL, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df263ef60a18bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS AI Architect</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, PySpark, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db11b97dc614b82</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f453eb1bd89d09d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Junior Developer - Python &amp; Go</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
+          <t>RDS, Spark, PySpark, Scala, Oracle, MySQL, Data Modeling, Star Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b08b09c902350587</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Oracle, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
+          <t>https://www.indeed.com/viewjob?jk=651024a294e974c0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e31041a5ff01e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Tableau Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
+          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>Tradeify</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
+          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Streamline Defense</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
+          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e31041a5ff01e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tableau Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Consultant, Product Architect (P&amp;C Data)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, Informatica PowerCenter, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0537b6f1de175b28</t>
+          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,89 +2631,89 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>ETL Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Streamline Defense</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Sr Java Backend - Miami</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4c09f4dfc51429</t>
+          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 2, DevOps</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
+          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
+          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
+          <t>Grid Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Architect (Hands on)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Burlington, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938814309f98f913</t>
+          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Grid Data Analyst</t>
+          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Hands on)</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
+          <t>Data Engineer Junior or Senior</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure and Databricks)</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af43569fb68ff56a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,29 +3251,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>eSentire</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Data &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ProFocus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eSentire</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data &amp; Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Senior Service Management Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Full Stack Software Engineer (Contract Role)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae8f41ca2bcca01</t>
+          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Advanced Software Architect (Remote - United States)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, RDS, Azure, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e39da103dc0a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=030ed8e9753c3192</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0edabd1040dd11</t>
+          <t>https://www.indeed.com/viewjob?jk=bae8f41ca2bcca01</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Advanced Software Architect (Remote - United States)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Branchburg, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, RDS, Azure, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=0e39da103dc0a30b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Technical Architect, Integration Development</t>
+          <t>Senior Full Stack Software Engineer (Contract Role)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0edabd1040dd11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sdq</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Branchburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffd021f83c93fff</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Solutions Architect 4</t>
+          <t>Technical Architect, Integration Development</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Hybrid)</t>
+          <t>Associate Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KnowBe4</t>
+          <t>Bealls Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Scala, PostgreSQL, MySQL, DynamoDB, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadf60f6511d26fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
+          <t>Integration Developer (Java) - JIDEV 26-07339</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Solutions Architect 4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,87 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Associate Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Bealls Inc.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Bradenton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Integration Developer (Java) - JIDEV 26-07339</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data - Archimedes</t>
+          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.6</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d62482ae7cddd2</t>
+          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer (Job Code: 1104)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Federal Soft Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, EMR, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b47572932e8bfd</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, Azure, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>StationMD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Maplewood, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>StationMD</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maplewood, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
+          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
+          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,129 +846,129 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
+          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Data</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cloudforce</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>National Harbor, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eBusiness Solutions Inc.</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,77 +1091,77 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2933456811155d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Sr Back-End Python SW Eng</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=6115b9c4717b463e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c93acf42a0d223</t>
+          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Java AWS Developer - Face to Face Interview</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Core Alliance Group Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=922392e2e4746be9</t>
+          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java AWS Developer - Face to Face Interview</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Core Alliance Group Inc.</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
+          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f715405c24533f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Canoe Platform Data / Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canoe Platform Data / Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>Solifi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
+          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f715405c24533f</t>
+          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Developer -AWS Python SQL Big Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Solifi</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
+          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Digital Site Reliability Sr Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HBase, Scala, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02dd332b5bab760b</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>WesTech Engineering, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WesTech Engineering, LLC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Junior Developer - Python &amp; Go</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
         </is>
       </c>
     </row>
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
+          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Tradeify</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Oracle, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651024a294e974c0</t>
+          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e31041a5ff01e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tableau Data Architect</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Streamline Defense</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Tableau Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tradeify</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,94 +2421,94 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
+          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Streamline Defense</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Data Engineer III</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
+          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
+          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
+          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Java Backend - Miami</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2, DevOps</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Power BI, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Grid Data Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,857 +2971,2397 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
+          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Hands on)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer Junior or Senior</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eSentire</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data &amp; Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Service Management Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
+          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=030ed8e9753c3192</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae8f41ca2bcca01</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Advanced Software Architect (Remote - United States)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, RDS, Azure, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e39da103dc0a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0edabd1040dd11</t>
+          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Branchburg, NJ, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Technical Architect, Integration Development</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Solutions Architect 4</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer - Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Imperial PFS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Mid Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>The Brite Group</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Finance</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mortenson Construction</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, SQL Server, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ETL Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sr Java Backend - Miami</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>_coderio</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Software Engineer 2, DevOps</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer, AI Platform</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Grid Data Analyst</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sumter Electric Cooperative, Inc</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Sumterville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Analytics &amp; BI with Tableau</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
         <v>10.4</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Spark, Oracle, ELT, MLflow, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dfc48a9ef7a026</t>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pacific Life</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Data Architect (Hands on)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Stratus</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>State Street</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Quincy, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Engineer Junior or Senior</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>South Florida Community Care Network</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Analytics Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>eSentire</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ProFocus</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Analytics Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Service Management Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Branchburg, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bealls Inc.</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Technical Architect, Integration Development</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Brown Advisory</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=030ed8e9753c3192</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>StationMD</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maplewood, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
+          <t>https://www.indeed.com/viewjob?jk=18acf0e8544b3a5b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>StationMD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Maplewood, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
+          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
+          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
         </is>
       </c>
     </row>
@@ -946,64 +946,64 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
+          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
+          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Back-End Python SW Eng</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6115b9c4717b463e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr Back-End Python SW Eng</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=6115b9c4717b463e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java AWS Developer - Face to Face Interview</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Core Alliance Group Inc.</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
+          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Java AWS Developer - Face to Face Interview</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Core Alliance Group Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f715405c24533f</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Canoe Platform Data / Integration Engineer</t>
+          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
+          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Canoe Platform Data / Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Solifi</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Solifi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Developer -AWS Python SQL Big Data</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
+          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
+          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer -AWS Python SQL Big Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
+          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WesTech Engineering, LLC</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>WesTech Engineering, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Junior Developer - Python &amp; Go</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>IO Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
+          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, Oracle, MySQL, Data Modeling, Star Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08b09c902350587</t>
+          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tradeify</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Spark, PySpark, Scala, Oracle, MySQL, Data Modeling, Star Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
+          <t>https://www.indeed.com/viewjob?jk=b08b09c902350587</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Tradeify</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
+          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Streamline Defense</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
         </is>
       </c>
     </row>
@@ -2428,35 +2428,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Streamline Defense</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
+          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
+          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
+          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
+          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
+          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
+          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
+          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
+          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
+          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
+          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
+          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
+          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
+          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
+          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
+          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
+          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Data Engineer III</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
+          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Finance</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mortenson Construction</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, SQL Server, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
+          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>Senior Data Engineer / Analytics Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr Java Backend - Miami</t>
+          <t>Senior Data Analyst - Finance</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Mortenson Construction</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, SQL Server, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
+          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Java Backend - Miami</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
+          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer 2, DevOps</t>
+          <t>ETL Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Software Engineer 2, DevOps</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Grid Data Analyst</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Palmer Holland</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westlake, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,42 +4651,42 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Grid Data Analyst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,67 +4696,67 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
+          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Hands on)</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer Junior or Senior</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Data Architect (Hands on)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Junior or Senior</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>eSentire</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data &amp; Platform Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
         </is>
       </c>
     </row>
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Service Management Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>eSentire</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Data &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ProFocus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Branchburg, NJ, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Senior Service Management Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Technical Architect, Integration Development</t>
+          <t>Senior Full Stack Software Engineer (Contract Role)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Branchburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,15 +5351,190 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Bealls Inc.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Technical Architect, Integration Development</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Brown Advisory</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Product Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Bristol, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=030ed8e9753c3192</t>
         </is>

--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
+          <t>Specialist Engineer- Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
+          <t>https://www.indeed.com/viewjob?jk=a967b71634e71edd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer (Job Code: 1104)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Federal Soft Systems</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, EMR, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b47572932e8bfd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer (Job Code: 1104)</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Federal Soft Systems</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Hadoop, Hive</t>
+          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, Azure, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b47572932e8bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=18acf0e8544b3a5b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>StationMD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Maplewood, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, Azure, Databricks, Blob Storage</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18acf0e8544b3a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>StationMD</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maplewood, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
+          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Kepler22 LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NorthStar Advisory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a103a483832a643b</t>
         </is>
       </c>
     </row>
@@ -981,54 +981,54 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
+          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
+          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Back-End Python SW Eng</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6115b9c4717b463e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Sr Back-End Python SW Eng</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=6115b9c4717b463e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java AWS Developer - Face to Face Interview</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Core Alliance Group Inc.</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911b4ea00661e78</t>
+          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd72966a9cf0f195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Administrator/ETL &amp; Data Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Dimension Tables, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00de8f5aef404a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Canoe Platform Data / Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canoe Platform Data / Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Solifi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Solifi</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
+          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer -AWS Python SQL Big Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer -AWS Python SQL Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Autonomous Lab</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Ginkgo BioWorks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
+          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WesTech Engineering, LLC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Dimensional Modeling, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff9d72c37ab8ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IO Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,77 +1816,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>rSTAR Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IO Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
+          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Developer - Python &amp; Go</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Spark, PySpark, Scala, Oracle, MySQL, Data Modeling, Star Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=b08b09c902350587</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, Oracle, MySQL, Data Modeling, Star Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08b09c902350587</t>
+          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Tableau Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tradeify</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
+          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Tradeify</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
+          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tableau Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Data Engineer III</t>
+          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7abd08cb282d025e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4c09f4dfc51429</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fcfcdc16ea146b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
+          <t>Sr Java Backend - Miami</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Finance</t>
+          <t>ETL Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mortenson Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, SQL Server, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Java Backend - Miami</t>
+          <t>Senior Data Engineer / Analytics Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
+          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>Senior Data Analyst - Finance</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mortenson Construction</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, SQL Server, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Grid Data Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Grid Data Analyst</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,52 +4721,52 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Six Feet Up Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Windermere, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
         </is>
       </c>
     </row>
@@ -4913,17 +4913,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>XoriantːUS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer Junior or Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Data Engineer Junior or Senior</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>eSentire</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,19 +5116,19 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data &amp; Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>eSentire</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,19 +5151,19 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Data &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>ProFocus</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Service Management Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
+          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Azure Cosmos DB, MLOps, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd86556e8fae62</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Full Stack Software Engineer (Contract Role)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Branchburg, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Senior Service Management Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Integration Developer (Java) - JIDEV 26-07339</t>
+          <t>SQL Server Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbf6df684aee028</t>
+          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Technical Architect, Integration Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Branchburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
+          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Associate Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bealls Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Technical Architect, Integration Development</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Brown Advisory</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,42 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=030ed8e9753c3192</t>
+          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Product Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Bristol, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Cloud Developer (AI/ML Integration)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kepler22 LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3945e37d35f435</t>
+          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kepler22 LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a103a483832a643b</t>
+          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
         </is>
       </c>
     </row>
@@ -981,64 +981,64 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
+          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb6fa8346777685</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Back-End Python SW Eng</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6115b9c4717b463e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
+          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd72966a9cf0f195</t>
+          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canoe Platform Data / Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brown Advisory</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5ac4383e90fa07</t>
+          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Solifi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Solifi</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
+          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer -AWS Python SQL Big Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Developer -AWS Python SQL Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Autonomous Lab</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Ginkgo BioWorks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
+          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Autonomous Lab</t>
+          <t>IO Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ginkgo BioWorks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,129 +1721,129 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>rSTAR Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IO Engineer</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>rSTAR Technologies</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junior Developer - Python &amp; Go</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Stevens Transport</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=078bbf0fc22f4951</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
+          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>Senior Data Warehouse Specialist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=94376982bbadef2c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Tradeify</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
+          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, Oracle, MySQL, Data Modeling, Star Schema, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08b09c902350587</t>
+          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tradeify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,122 +2341,122 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
+          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer (Req. #001109)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Streamline Defense</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
+          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
+          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
+          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
+          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
+          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
+          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
+          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
+          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
+          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
+          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
+          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
+          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
+          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
+          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
+          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
+          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
+          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4c09f4dfc51429</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4c09f4dfc51429</t>
+          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 2, DevOps</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea1e8505433b954b</t>
+          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Java Backend - Miami</t>
+          <t>ETL Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2e30ac46648130</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palmer Holland</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Westlake, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Finance</t>
+          <t>Grid Data Analyst</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mortenson Construction</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, SQL Server, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer / Analytics Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
+          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer 2, DevOps</t>
+          <t>Machine Learning Engineer| AI - US</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,77 +4546,77 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Scala, dbt, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=46b7a8d8a75a3102</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Six Feet Up Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Windermere, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,102 +4626,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Palmer Holland</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Westlake, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Architect (Hands on)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Grid Data Analyst</t>
+          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Six Feet Up Inc.</t>
+          <t>XoriantːUS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Windermere, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Hands on)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
+          <t>Data Engineer Junior or Senior</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>XoriantːUS</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer Junior or Senior</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>eSentire</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,19 +5046,19 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Data &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>ProFocus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Technical Architect - SD .Net</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>eSentire</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, NoSQL, Maven, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=db9f9b4a776fe557</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data &amp; Platform Engineer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Azure Cosmos DB, MLOps, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd86556e8fae62</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Senior Service Management Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366c81cd8f5e4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>SQL Server Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Azure Cosmos DB, MLOps, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd86556e8fae62</t>
+          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Branchburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Contract Role)</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,225 +5351,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94d9392fb73f5bb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Service Management Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>O'Fallon, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SQL Server Developer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>CloudSecurityweb</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Branchburg, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Associate Developer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Bealls Inc.</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Bradenton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cc4c50738fa61</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Technical Architect, Integration Development</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Brown Advisory</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, SQL</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d41ed71ea14382d</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Product Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Bristol, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
         </is>

--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>StationMD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Maplewood, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18acf0e8544b3a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>StationMD</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maplewood, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
+          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Kepler22 LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
+          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kepler22 LLC</t>
+          <t>NorthStar Advisory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NorthStar Advisory</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Application Integration Architect (MuleSoft)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Matrix Global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Google Cloud Platform, GCP, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
+          <t>https://www.indeed.com/viewjob?jk=2b723b38fa8fbc83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec47147e2ed177aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Python Sr Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,50 +1073,50 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f9fb6b17436490</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eaa505c1c3eb5b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09394d29337f2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Fullstack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc921b51064b64c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Solifi</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=babc3334dbca037a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IO Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>rSTAR Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rSTAR Technologies</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Junior Developer - Python &amp; Go</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Stevens Transport</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stevens Transport</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=078bbf0fc22f4951</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Warehouse Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
+          <t>https://www.indeed.com/viewjob?jk=94376982bbadef2c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078bbf0fc22f4951</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
+          <t>https://www.indeed.com/viewjob?jk=810aff76fcea7f08</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94376982bbadef2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Tradeify</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tradeify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,174 +2201,174 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e55b50dfb3e575</t>
+          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer (Req. #001109)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c02c2c6f52869df</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd1148f8c45344e</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tableau Data Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46da1e8652df6dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Req. #001109)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
+          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
+          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
+          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
+          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
+          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
+          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
+          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
+          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
+          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
+          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
+          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
+          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
+          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
+          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
+          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
+          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
+          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
+          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
+          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
+          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
+          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Data Engineer III</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd58ffff39c916df</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>JAVA Developer with Python</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
+          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4c09f4dfc51429</t>
+          <t>https://www.indeed.com/viewjob?jk=89b20777bda6e070</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UI Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer 2, DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>Software Engineer 2, DevOps</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>ETL Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Palmer Holland</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Westlake, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Palmer Holland</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Westlake, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Grid Data Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sumter Electric Cooperative, Inc</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sumterville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Experienced Solution Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Six Feet Up Inc.</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Windermere, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Six Feet Up Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Windermere, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
+          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Architect (Hands on)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, MongoDB, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>XoriantːUS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, PostgreSQL, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>XoriantːUS</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer Junior or Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Data Engineer Junior or Senior</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>eSentire</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data &amp; Platform Engineer</t>
+          <t>GCP Data Architect (Migration)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, ETL, ELT, Power BI, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f6c0c52409982</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6d8e7cc07815dc</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Associate Technical Architect - SD .Net</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, NoSQL, Maven, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=db9f9b4a776fe557</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - SD .Net</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, NoSQL, Maven, Git</t>
+          <t>RDS, Azure, Databricks, Azure Cosmos DB, MLOps, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9f9b4a776fe557</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd86556e8fae62</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Azure Cosmos DB, MLOps, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd86556e8fae62</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfc2fbc843f882c</t>
         </is>
       </c>
     </row>
@@ -5292,76 +5292,6 @@
       <c r="G139" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Branchburg, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, NoSQL, ETL, Power BI, Tableau, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1bf3669af20ddd</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Product Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Bristol, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-18.xlsx
+++ b/results/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Databricks Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, Azure, Databricks, Blob Storage</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8dce8d9e924a15a0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>StationMD</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Maplewood, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, Azure, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>StationMD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Maplewood, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Hive, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1fc723cf2dcf75</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Sr. Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
+          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1040994c17347d28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kepler22 LLC</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=953fdc46403c9c1c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kepler22 LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dde168972f7d9f8a</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NorthStar Advisory</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>NorthStar Advisory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
+          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Application Integration Architect (MuleSoft)</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Matrix Global</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Google Cloud Platform, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, NoSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b723b38fa8fbc83</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Application Integration Architect (MuleSoft)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Matrix Global</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Google Cloud Platform, GCP, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=2b723b38fa8fbc83</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Python Sr Developer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, RDS, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eaa505c1c3eb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Python Sr Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eaa505c1c3eb5b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BetMGM LLC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
+          <t>https://www.indeed.com/viewjob?jk=da83e15313b5387c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fullstack Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc921b51064b64c</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea638d0883296e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+          <t>Fullstack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc921b51064b64c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,104 +1466,104 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Blob Storage, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Developer -AWS Python SQL Big Data</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
+          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
+          <t>https://www.indeed.com/viewjob?jk=600c14750e4f5e4f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer -AWS Python SQL Big Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5a95adb8844b24</t>
+          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Autonomous Lab</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ginkgo BioWorks</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb3631b88884d67</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior Software Engineer, Autonomous Lab</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rSTAR Technologies</t>
+          <t>Ginkgo BioWorks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>rSTAR Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>SQS, RDS, Azure, Scala, Kafka, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0222ee1ad2ca4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, Cassandra, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
+          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
+          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stevens Transport</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7576a00a2fad13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Scentsy</t>
+          <t>Stevens Transport</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5a3b6fdcf0fb47</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Scentsy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, RDS, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=9b137e45bf5f06dd</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
+          <t>https://www.indeed.com/viewjob?jk=810aff76fcea7f08</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Specialist</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94376982bbadef2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Oracle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=210a28a4f5a7d059</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=810aff76fcea7f08</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
@@ -2183,52 +2183,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Senior Software Engineer (Req. #001109)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Req. #001109)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, PySpark, Scala, Kafka, Oracle, Power BI, Tableau, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1c33a51cd10735</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5d0f3636ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7246bfe0658b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f45158705902e48</t>
+          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79bb28ee587ba57</t>
+          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e455d2ef83c7d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ae1fb924c01ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59692155707137c4</t>
+          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302a91f345cccc1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0d58e397fd4549</t>
+          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe33d670995e8e14</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5d55387944066f</t>
+          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2affa7be6577d401</t>
+          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7760cd34fc66c07</t>
+          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a97657de2858ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a7f903d6c4547b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f0a41d63e9b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eda8f1e8211274</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ebb938bf679dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122a9e11def461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9dcff536361036</t>
+          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511064acfbd9b012</t>
+          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deac36aa4f5b9cff</t>
+          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddbf0efe4c741e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c638a1dbd6b5f2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f1fbd0b58148ef</t>
+          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fca3b7950cf092</t>
+          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c14578d27ff5bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2659cf2c525d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0627ab21a2b7bf2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce49b5dae800b39</t>
+          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d2759dcd310614</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3ae2f19b52020f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1d983b95c40b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567bafbd0488971</t>
+          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b850ab6975098684</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6d774af6b0bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5318752b9d151652</t>
+          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32028fd97b970e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7780edf635f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e4d5d5b154e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a77915aa0ca5815</t>
+          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffc5412b6d74d51</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc3418fad5b593d</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc016909bf5b841</t>
+          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df3f543498e5037</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6417fbc759bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccc616531f13779</t>
+          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283efb3dccc0304</t>
+          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53cfa544c3dedac3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Databricks Migration Engineer – Hybrid- Laurel, MD</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f8b1a3c45c2297</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5d1120e69e2978</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Data Engineer III</t>
+          <t>Sr. Software Engineer, AI Native</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>JAVA Developer with Python</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Palmer Holland</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westlake, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89b20777bda6e070</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
+          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UI Software Developer</t>
+          <t>ETL Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae18f46c8596540</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer 2, DevOps</t>
+          <t>UI Software Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Telit Wireless Solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=48589f399d5e9f07</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ETL Architect</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, YARN, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e1d958ff09db55</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer / Analytics Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Palmer Holland</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Westlake, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, ELT, MLOps, MLflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
+          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Machine Learning Engineer| AI - US</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Scala, dbt, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=46b7a8d8a75a3102</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
+          <t>Experienced Solution Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer| AI - US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Six Feet Up Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Windermere, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Scala, dbt, Power BI, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b7a8d8a75a3102</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Experienced Solution Architect</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7addd26aa01f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Six Feet Up Inc.</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Windermere, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f51e7d95dba89e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>XoriantːUS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2754840bc98a3a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f484d19ecc08455</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>XoriantːUS</t>
+          <t>COLORADO SCHOOL OF MINES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Oozie, Spark, Scala, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebfd4178b2db6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Horizon Surgical Systems</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9c92b446fa7e41</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>COLORADO SCHOOL OF MINES</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e36579a37632f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FULLTHROTTLE</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, CI/CD, CodeBuild, Terraform</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Junior or Senior</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e252cb63f4e5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer Junior or Senior</t>
+          <t>GCP Data Architect (Migration)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Snowflake, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6d8e7cc07815dc</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Associate Technical Architect - SD .Net</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, NoSQL, Maven, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143a41fe2cf86e21</t>
+          <t>https://www.indeed.com/viewjob?jk=db9f9b4a776fe557</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, EMR, Spark, PySpark, Scala, Polars, Data Modeling, CI/CD, Airflow, Python</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfc2fbc843f882c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GCP Data Architect (Migration)</t>
+          <t>Senior Quality Engineer -Test Governance &amp; Standards</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6d8e7cc07815dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf4dab9e3ca16af</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - SD .Net</t>
+          <t>Senior Service Management Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, NoSQL, Maven, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9f9b4a776fe557</t>
+          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>SQL Server Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Azure Cosmos DB, MLOps, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd86556e8fae62</t>
+          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Shopify Architect</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,122 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfc2fbc843f882c</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Service Management Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>O'Fallon, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68768630430d6a89</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>SQL Server Developer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CloudSecurityweb</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Scala, Kafka, SQL Server, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48fa998d6825ef93</t>
         </is>
       </c>
     </row>
